--- a/RUC/RUC_Producto.xlsx
+++ b/RUC/RUC_Producto.xlsx
@@ -2801,13 +2801,13 @@
         <v>0.0729388798091555</v>
       </c>
       <c r="L2" s="2">
-        <v>112.2262160580291</v>
+        <v>111.7005326165214</v>
       </c>
       <c r="M2" s="2">
-        <v>1.63713089689858</v>
+        <v>1.629462344627021</v>
       </c>
       <c r="N2" s="2">
-        <v>0.08185654484492902</v>
+        <v>0.08147311723135107</v>
       </c>
     </row>
     <row r="3" spans="1:14">
